--- a/data/WA_GMA_PW_Surveying Data Collection.xlsx
+++ b/data/WA_GMA_PW_Surveying Data Collection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DevMain\Projects\WS_WaterProj_repo\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F3359C-CB96-49A2-9EEB-64E4FCA74918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E056D5F-9298-4A8E-BB7A-C7570800BAE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{E5EAAB83-6498-48CA-A5B9-4E9E8D7EA133}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="1" activeTab="1" xr2:uid="{E5EAAB83-6498-48CA-A5B9-4E9E8D7EA133}"/>
   </bookViews>
   <sheets>
     <sheet name="Full survey table" sheetId="54" r:id="rId1"/>
@@ -61,7 +61,6 @@
     <sheet name="Rosalia" sheetId="45" r:id="rId46"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -2583,7 +2582,34 @@
     <t>Columns BC &amp; BF —  Full Town Debt and Capital &amp; Bonded Debt figures for all surveyed jurisdictions (entity-level citations in column BH)</t>
   </si>
   <si>
-    <t>APA 7th Edition Citation</t>
+    <t>Debt figures &lt;FI&gt; APA 7th Edition Citations</t>
+  </si>
+  <si>
+    <t>Based upon their consumption beyond their alloted amount. Asotin has a water system that gives alloted amounts of water to residents, excess is handled  by the utilities district.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Been public works director for year in a half 60 with 40 years in construction, think its helped a lot with problem solving skills. 125 year old town, 6-7 years ago case of embezzlment, now we get audited every year. Young mayor, fantastic city clerk. main source of leaks is steel pipes, pumping 130m gallons a year, wasting 27%. 6 inch pvc, wasting a lot of money on contractors. </t>
+  </si>
+  <si>
+    <t>When I do the budgetting for water, what we are looking at is how expenditures are changing over the last year. Anything that we can forsee, like gas prices jumping, anything we think will be an impact we try to add that as a thought process for our budget.</t>
+  </si>
+  <si>
+    <t>our fees are pretty high. Big variety of SDCs. We do whole electric systm, water is more localized. Stevenson and north bonnevile do their own. Skamania landing has their own water system. Rural systems do their own thing. They sometimes hire out contracotrs if they are real small. We are taking a preactive approach for repairs and older things breaking.</t>
+  </si>
+  <si>
+    <t>Skamania county public utilities district. Both towns manage their own. General water utilities for other communities is the skamnaia county public utilities district. 5094275126. city of bonneville Cody rosander (5094275970). Not sure who to contact for bonneville.</t>
+  </si>
+  <si>
+    <t>Riley Bunnell, Public Works Directior</t>
+  </si>
+  <si>
+    <t>Yes we have, a little more than 10 years ago we switched to ground wells from surface waters. We expanded our system to accomodate for that .</t>
+  </si>
+  <si>
+    <t>Yes we use a GIS tool. We have an asset management system. Its lucidy, a work order and asset management program (Not gis). As far as our system value, we produce and maintain water and sewer system plans that go into more detail on the value of the system. that is the doc that guides more of our long term planning.</t>
+  </si>
+  <si>
+    <t>Chicago (Notes-Bibliography) Citation</t>
   </si>
   <si>
     <r>
@@ -2592,7 +2618,7 @@
         <rFont val="Arial"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Washington State Department of Commerce. (n.d.). </t>
+      <t xml:space="preserve">Washington State Department of Commerce. </t>
     </r>
     <r>
       <rPr>
@@ -2601,7 +2627,7 @@
         <rFont val="Arial"/>
         <charset val="1"/>
       </rPr>
-      <t>A guide to the periodic update process under the Growth Management Act.</t>
+      <t>A Guide to the Periodic Update Process under the Growth Management Act.</t>
     </r>
     <r>
       <rPr>
@@ -2609,7 +2635,7 @@
         <rFont val="Arial"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve"> Yakima County. Retrieved May 25, 2026, from https://www.yakimacounty.us/DocumentCenter/View/35541/GMA-UPDATE-tab---A-Guide-to-the-Periodic-Update-Process-under-the-GMA</t>
+      <t xml:space="preserve"> Hosted by Yakima County. Accessed May 25, 2026. https://www.yakimacounty.us/DocumentCenter/View/35541/GMA-UPDATE-tab---A-Guide-to-the-Periodic-Update-Process-under-the-GMA.</t>
     </r>
   </si>
   <si>
@@ -2619,7 +2645,7 @@
         <rFont val="Arial"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Washington State Department of Commerce. (2025, June 25). </t>
+      <t xml:space="preserve">Washington State Department of Commerce. </t>
     </r>
     <r>
       <rPr>
@@ -2628,7 +2654,7 @@
         <rFont val="Arial"/>
         <charset val="1"/>
       </rPr>
-      <t>Comprehensive planning under the Growth Management Act</t>
+      <t>Comprehensive Planning under the Growth Management Act.</t>
     </r>
     <r>
       <rPr>
@@ -2636,8 +2662,17 @@
         <rFont val="Arial"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve"> [PowerPoint slides]. Whitman County. https://www.whitmancounty.gov/DocumentCenter/View/10602/Comprehensive-Planning-Under-the-Growth-Management-Act---2025-06-25-PDF</t>
+      <t xml:space="preserve"> PowerPoint presentation hosted by Whitman County, June 25, 2025. https://www.whitmancounty.gov/DocumentCenter/View/10602/Comprehensive-Planning-Under-the-Growth-Management-Act---2025-06-25-PDF.</t>
     </r>
+  </si>
+  <si>
+    <t>MRSC. “Growth Management Act Basics.” Last modified February 25, 2026. https://mrsc.org/explore-topics/planning/gma/growth-management-act-basics.</t>
+  </si>
+  <si>
+    <t>Growth Management Act, Wash. Rev. Code ch. 36.70A (2026). https://app.leg.wa.gov/rcw/default.aspx?cite=36.70A.</t>
+  </si>
+  <si>
+    <t>Futurewise. “About the GMA.” Accessed May 25, 2026. https://futurewise.org/about-the-gma/.</t>
   </si>
   <si>
     <r>
@@ -2646,7 +2681,7 @@
         <rFont val="Arial"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Municipal Research and Services Center of Washington. (2026, February 25). </t>
+      <t xml:space="preserve">Washington State Department of Commerce. </t>
     </r>
     <r>
       <rPr>
@@ -2655,7 +2690,7 @@
         <rFont val="Arial"/>
         <charset val="1"/>
       </rPr>
-      <t>Growth management act basics.</t>
+      <t>Long Range Planning in Washington State.</t>
     </r>
     <r>
       <rPr>
@@ -2663,11 +2698,8 @@
         <rFont val="Arial"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve"> https://mrsc.org/explore-topics/planning/gma/growth-management-act-basics</t>
+      <t xml:space="preserve"> Hosted by City of Poulsbo. Accessed May 25, 2026. https://poulsbo.gov/wp-content/uploads/2018/12/PlanninginWAState.pdf.</t>
     </r>
-  </si>
-  <si>
-    <t>Growth Management Act, Wash. Rev. Code § 36.70A (2026). https://app.leg.wa.gov/RCW/default.aspx?cite=36.70A</t>
   </si>
   <si>
     <r>
@@ -2676,7 +2708,7 @@
         <rFont val="Arial"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Futurewise. (n.d.). </t>
+      <t xml:space="preserve">Washington State Legislature, Senate Committee on Ways &amp; Means. </t>
     </r>
     <r>
       <rPr>
@@ -2685,7 +2717,7 @@
         <rFont val="Arial"/>
         <charset val="1"/>
       </rPr>
-      <t>About the GMA.</t>
+      <t>Senate Bill Report: E2SHB 1241.</t>
     </r>
     <r>
       <rPr>
@@ -2693,7 +2725,7 @@
         <rFont val="Arial"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve"> Retrieved May 25, 2026, from https://futurewise.org/about-the-gma/</t>
+      <t xml:space="preserve"> 2021. https://lawfilesext.leg.wa.gov/biennium/2021-22/Pdf/Bill%20Reports/Senate/1241-S.E%20SBR%20WM%20OC%2021.pdf.</t>
     </r>
   </si>
   <si>
@@ -2703,7 +2735,7 @@
         <rFont val="Arial"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Washington State Department of Commerce. (n.d.). </t>
+      <t xml:space="preserve">Washington State Office of Financial Management. </t>
     </r>
     <r>
       <rPr>
@@ -2712,7 +2744,7 @@
         <rFont val="Arial"/>
         <charset val="1"/>
       </rPr>
-      <t>Long range planning in Washington State</t>
+      <t>April 1 Postcensal Estimates of Population, 1960–Present.</t>
     </r>
     <r>
       <rPr>
@@ -2720,7 +2752,7 @@
         <rFont val="Arial"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve"> [PDF]. City of Poulsbo. Retrieved May 25, 2026, from https://poulsbo.gov/wp-content/uploads/2018/12/PlanninginWAState.pdf</t>
+      <t xml:space="preserve"> Data set. Accessed May 25, 2026. https://ofm.wa.gov/wp-content/uploads/sites/default/files/public/dataresearch/pop/april1/hseries/ofm_april1_postcensal_estimates_pop_1960-present.xlsx.</t>
     </r>
   </si>
   <si>
@@ -2730,7 +2762,7 @@
         <rFont val="Arial"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Washington State Legislature, Senate Committee on Ways &amp; Means. (2021). </t>
+      <t xml:space="preserve">Washington State Auditor’s Office. </t>
     </r>
     <r>
       <rPr>
@@ -2739,7 +2771,7 @@
         <rFont val="Arial"/>
         <charset val="1"/>
       </rPr>
-      <t>Senate bill report: E2SHB 1241.</t>
+      <t>Financial Intelligence Tool (FIT).</t>
     </r>
     <r>
       <rPr>
@@ -2747,89 +2779,8 @@
         <rFont val="Arial"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve"> https://app.leg.wa.gov/documents/billdocs/2021-22/Htm/Bill%20Reports/Senate/1241-S.E%20SBR%20WM%20OC%2021.htm</t>
+      <t xml:space="preserve"> Data set. Accessed May 25, 2026. https://portal.sao.wa.gov/FIT.</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Washington State Office of Financial Management. (n.d.). </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
-      </rPr>
-      <t>April 1 postcensal estimates of population, 1960–present</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> [Data set]. Retrieved May 25, 2026, from https://ofm.wa.gov/wp-content/uploads/sites/default/files/public/dataresearch/pop/april1/hseries/ofm_april1_postcensal_estimates_pop_1960-present.xlsx</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Washington State Auditor's Office. (n.d.). </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
-      </rPr>
-      <t>Financial Intelligence Tool (FIT)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> [Data set]. Retrieved May 25, 2026, from https://portal.sao.wa.gov/FIT</t>
-    </r>
-  </si>
-  <si>
-    <t>Debt figures &lt;FI&gt; APA 7th Edition Citations</t>
-  </si>
-  <si>
-    <t>Based upon their consumption beyond their alloted amount. Asotin has a water system that gives alloted amounts of water to residents, excess is handled  by the utilities district.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Been public works director for year in a half 60 with 40 years in construction, think its helped a lot with problem solving skills. 125 year old town, 6-7 years ago case of embezzlment, now we get audited every year. Young mayor, fantastic city clerk. main source of leaks is steel pipes, pumping 130m gallons a year, wasting 27%. 6 inch pvc, wasting a lot of money on contractors. </t>
-  </si>
-  <si>
-    <t>When I do the budgetting for water, what we are looking at is how expenditures are changing over the last year. Anything that we can forsee, like gas prices jumping, anything we think will be an impact we try to add that as a thought process for our budget.</t>
-  </si>
-  <si>
-    <t>our fees are pretty high. Big variety of SDCs. We do whole electric systm, water is more localized. Stevenson and north bonnevile do their own. Skamania landing has their own water system. Rural systems do their own thing. They sometimes hire out contracotrs if they are real small. We are taking a preactive approach for repairs and older things breaking.</t>
-  </si>
-  <si>
-    <t>Skamania county public utilities district. Both towns manage their own. General water utilities for other communities is the skamnaia county public utilities district. 5094275126. city of bonneville Cody rosander (5094275970). Not sure who to contact for bonneville.</t>
-  </si>
-  <si>
-    <t>Riley Bunnell, Public Works Directior</t>
-  </si>
-  <si>
-    <t>Yes we have, a little more than 10 years ago we switched to ground wells from surface waters. We expanded our system to accomodate for that .</t>
-  </si>
-  <si>
-    <t>Yes we use a GIS tool. We have an asset management system. Its lucidy, a work order and asset management program (Not gis). As far as our system value, we produce and maintain water and sewer system plans that go into more detail on the value of the system. that is the doc that guides more of our long term planning.</t>
   </si>
 </sst>
 </file>
@@ -3991,6 +3942,12 @@
     <xf numFmtId="0" fontId="17" fillId="15" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4016,12 +3973,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5485,86 +5436,86 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:60" x14ac:dyDescent="0.35">
-      <c r="A1" s="122"/>
-      <c r="B1" s="123"/>
-      <c r="C1" s="124" t="s">
+      <c r="A1" s="124"/>
+      <c r="B1" s="125"/>
+      <c r="C1" s="126" t="s">
         <v>578</v>
       </c>
-      <c r="D1" s="125"/>
-      <c r="E1" s="129"/>
-      <c r="F1" s="126" t="s">
+      <c r="D1" s="127"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="128" t="s">
         <v>558</v>
       </c>
-      <c r="G1" s="127"/>
-      <c r="H1" s="128"/>
-      <c r="I1" s="119" t="s">
+      <c r="G1" s="129"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="121" t="s">
         <v>559</v>
       </c>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="130" t="s">
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="123"/>
+      <c r="Q1" s="132" t="s">
         <v>560</v>
       </c>
-      <c r="R1" s="125"/>
-      <c r="S1" s="125"/>
-      <c r="T1" s="129"/>
-      <c r="U1" s="124" t="s">
+      <c r="R1" s="127"/>
+      <c r="S1" s="127"/>
+      <c r="T1" s="131"/>
+      <c r="U1" s="126" t="s">
         <v>561</v>
       </c>
-      <c r="V1" s="125"/>
-      <c r="W1" s="125"/>
-      <c r="X1" s="125"/>
-      <c r="Y1" s="125"/>
-      <c r="Z1" s="125"/>
-      <c r="AA1" s="125"/>
-      <c r="AB1" s="125"/>
-      <c r="AC1" s="129"/>
-      <c r="AD1" s="124" t="s">
+      <c r="V1" s="127"/>
+      <c r="W1" s="127"/>
+      <c r="X1" s="127"/>
+      <c r="Y1" s="127"/>
+      <c r="Z1" s="127"/>
+      <c r="AA1" s="127"/>
+      <c r="AB1" s="127"/>
+      <c r="AC1" s="131"/>
+      <c r="AD1" s="126" t="s">
         <v>562</v>
       </c>
-      <c r="AE1" s="125"/>
-      <c r="AF1" s="125"/>
-      <c r="AG1" s="125"/>
-      <c r="AH1" s="125"/>
-      <c r="AI1" s="125"/>
-      <c r="AJ1" s="125"/>
-      <c r="AK1" s="125"/>
-      <c r="AL1" s="125"/>
-      <c r="AM1" s="129"/>
-      <c r="AN1" s="124" t="s">
+      <c r="AE1" s="127"/>
+      <c r="AF1" s="127"/>
+      <c r="AG1" s="127"/>
+      <c r="AH1" s="127"/>
+      <c r="AI1" s="127"/>
+      <c r="AJ1" s="127"/>
+      <c r="AK1" s="127"/>
+      <c r="AL1" s="127"/>
+      <c r="AM1" s="131"/>
+      <c r="AN1" s="126" t="s">
         <v>563</v>
       </c>
-      <c r="AO1" s="125"/>
-      <c r="AP1" s="125"/>
-      <c r="AQ1" s="125"/>
-      <c r="AR1" s="125"/>
-      <c r="AS1" s="129"/>
-      <c r="AT1" s="124" t="s">
+      <c r="AO1" s="127"/>
+      <c r="AP1" s="127"/>
+      <c r="AQ1" s="127"/>
+      <c r="AR1" s="127"/>
+      <c r="AS1" s="131"/>
+      <c r="AT1" s="126" t="s">
         <v>564</v>
       </c>
-      <c r="AU1" s="125"/>
-      <c r="AV1" s="125"/>
-      <c r="AW1" s="125"/>
-      <c r="AX1" s="125"/>
-      <c r="AY1" s="125"/>
-      <c r="AZ1" s="124" t="s">
+      <c r="AU1" s="127"/>
+      <c r="AV1" s="127"/>
+      <c r="AW1" s="127"/>
+      <c r="AX1" s="127"/>
+      <c r="AY1" s="127"/>
+      <c r="AZ1" s="126" t="s">
         <v>565</v>
       </c>
-      <c r="BA1" s="125"/>
-      <c r="BB1" s="125"/>
-      <c r="BC1" s="119" t="s">
+      <c r="BA1" s="127"/>
+      <c r="BB1" s="127"/>
+      <c r="BC1" s="121" t="s">
         <v>633</v>
       </c>
-      <c r="BD1" s="120"/>
-      <c r="BE1" s="120"/>
-      <c r="BF1" s="120"/>
-      <c r="BG1" s="120"/>
-      <c r="BH1" s="121"/>
+      <c r="BD1" s="122"/>
+      <c r="BE1" s="122"/>
+      <c r="BF1" s="122"/>
+      <c r="BG1" s="122"/>
+      <c r="BH1" s="123"/>
     </row>
     <row r="2" spans="1:60" ht="69" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="28" t="s">
@@ -5745,7 +5696,7 @@
         <v>744</v>
       </c>
       <c r="BH2" s="50" t="s">
-        <v>772</v>
+        <v>762</v>
       </c>
     </row>
     <row r="3" spans="1:60" ht="137.5" x14ac:dyDescent="0.35">
@@ -6614,7 +6565,7 @@
       </c>
       <c r="D9" s="53"/>
       <c r="E9" s="40" t="s">
-        <v>778</v>
+        <v>768</v>
       </c>
       <c r="F9" s="34" t="s">
         <v>311</v>
@@ -8920,7 +8871,7 @@
       </c>
       <c r="AY26" s="51"/>
       <c r="AZ26" s="45" t="s">
-        <v>775</v>
+        <v>765</v>
       </c>
       <c r="BA26" s="30"/>
       <c r="BB26" s="51" t="s">
@@ -10164,7 +10115,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="35" spans="1:60" ht="187.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:60" ht="175" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>230</v>
       </c>
@@ -10320,10 +10271,10 @@
       </c>
       <c r="AY35" s="47"/>
       <c r="AZ35" s="58" t="s">
-        <v>776</v>
+        <v>766</v>
       </c>
       <c r="BA35" s="29" t="s">
-        <v>777</v>
+        <v>767</v>
       </c>
       <c r="BB35" s="47" t="s">
         <v>434</v>
@@ -12722,7 +12673,7 @@
       </c>
       <c r="B31" s="16"/>
       <c r="C31" s="16" t="s">
-        <v>774</v>
+        <v>764</v>
       </c>
     </row>
   </sheetData>
@@ -14500,31 +14451,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="120" t="s">
         <v>607</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
+      <c r="F1" s="120"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="131" t="s">
+      <c r="A2" s="119" t="s">
         <v>606</v>
       </c>
-      <c r="B2" s="131"/>
-      <c r="C2" s="131"/>
-      <c r="D2" s="131"/>
-      <c r="E2" s="131"/>
-      <c r="F2" s="131"/>
+      <c r="B2" s="119"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="119"/>
     </row>
     <row r="4" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="106" t="s">
         <v>605</v>
       </c>
       <c r="B4" s="106" t="s">
-        <v>762</v>
+        <v>771</v>
       </c>
       <c r="C4" s="106" t="s">
         <v>604</v>
@@ -14544,7 +14495,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="108" t="s">
-        <v>763</v>
+        <v>772</v>
       </c>
       <c r="C5" s="109" t="s">
         <v>600</v>
@@ -14564,7 +14515,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="112" t="s">
-        <v>764</v>
+        <v>773</v>
       </c>
       <c r="C6" s="113" t="s">
         <v>598</v>
@@ -14584,7 +14535,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="108" t="s">
-        <v>765</v>
+        <v>774</v>
       </c>
       <c r="C7" s="109" t="s">
         <v>595</v>
@@ -14604,7 +14555,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="112" t="s">
-        <v>766</v>
+        <v>775</v>
       </c>
       <c r="C8" s="113" t="s">
         <v>585</v>
@@ -14624,7 +14575,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="108" t="s">
-        <v>767</v>
+        <v>776</v>
       </c>
       <c r="C9" s="109" t="s">
         <v>590</v>
@@ -14644,7 +14595,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="112" t="s">
-        <v>768</v>
+        <v>777</v>
       </c>
       <c r="C10" s="113" t="s">
         <v>588</v>
@@ -14664,7 +14615,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="108" t="s">
-        <v>769</v>
+        <v>778</v>
       </c>
       <c r="C11" s="109" t="s">
         <v>585</v>
@@ -14684,7 +14635,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="112" t="s">
-        <v>770</v>
+        <v>779</v>
       </c>
       <c r="C12" s="113" t="s">
         <v>755</v>
@@ -14704,7 +14655,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="108" t="s">
-        <v>771</v>
+        <v>780</v>
       </c>
       <c r="C13" s="116" t="s">
         <v>758</v>
@@ -17671,10 +17622,10 @@
       <c r="B1" s="134"/>
       <c r="C1" s="77"/>
       <c r="D1" s="133"/>
-      <c r="E1" s="125"/>
-      <c r="F1" s="125"/>
-      <c r="G1" s="125"/>
-      <c r="H1" s="129"/>
+      <c r="E1" s="127"/>
+      <c r="F1" s="127"/>
+      <c r="G1" s="127"/>
+      <c r="H1" s="131"/>
     </row>
     <row r="2" spans="1:14" ht="78" x14ac:dyDescent="0.35">
       <c r="A2" s="37" t="s">
@@ -26719,7 +26670,7 @@
         <v>405</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>773</v>
+        <v>763</v>
       </c>
       <c r="D30" s="16"/>
     </row>
@@ -27049,7 +27000,7 @@
         <v>311</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>779</v>
+        <v>769</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="116" x14ac:dyDescent="0.35">
@@ -27080,7 +27031,7 @@
         <v>311</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>780</v>
+        <v>770</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
